--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
   <si>
     <t>Sound/Voice_Pug_1_I_WantToEatPizza</t>
   </si>
@@ -105,45 +105,1673 @@
     <t>dialogue_mainstream_1_1_200</t>
   </si>
   <si>
+    <t>SelectionDialogueIdList</t>
+  </si>
+  <si>
+    <t>dialogue_mainstream_2_1_100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_2_1_200</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_2_1_300</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>새로운 세계에 접속 하셨습니다…&lt;np&gt;여긴 꿈속 세상입니다.&lt;np&gt;여기서 탈출할 방법을 찾아야 합니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>저 멀리 무언가 격렬하게 움직이고 있습니다...&lt;np&gt;자세히 살펴보니 잔뜩 흥분한 슬라임이었습니다!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>저 슬라임에게 간다면 탈출할 방법이 있을지도 모른다는 생각에 다가가기로 결정했습니다!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>dialogue_mainstream_1_1_100</t>
-  </si>
-  <si>
-    <t>SelectionDialogueIdList</t>
-  </si>
-  <si>
-    <t>dialogue_mainstream_2_1_100</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_mainstream_2_1_200</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>dialogue_mainstream_2_1_300</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>새로운 세계에 접속 하셨습니다…&lt;np&gt;여긴 꿈속 세상입니다.&lt;np&gt;여기서 탈출할 방법을 찾아야 합니다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>저 멀리 무언가 격렬하게 움직이고 있습니다...&lt;np&gt;자세히 살펴보니 잔뜩 흥분한 슬라임이었습니다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>저 슬라임에게 간다면 탈출할 방법이 있을지도 모른다는 생각에 다가가기로 결정했습니다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_intro_1_100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_intro_1_102</t>
+  </si>
+  <si>
+    <t>dialogue_intro_1_103</t>
+  </si>
+  <si>
+    <t>dialogue_intro_1_104</t>
+  </si>
+  <si>
+    <t>dialogue_intro_1_105</t>
+  </si>
+  <si>
+    <t>(하품) 후아암…오늘도 완벽하게 아무것도 안 했다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 꿈은 오직 하나…아무것도 안 해도 통장에 돈이 썩어 넘치는 '돈 많은 백수'가 되는 것뿐인데…</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>현실은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잔고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이대로는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조만간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굶어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>죽겠어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!!</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_intro_1_101</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_intro_1_102</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국왕의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>특별</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>공고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나이가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>들어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기력이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쇠한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국왕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>폐하께서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>전설의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>황금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>찾으신다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사과를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가져오는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자에게는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>평생</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>먹고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>막대한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>금은보화와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영지를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하사하겠노라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>……</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이거다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!!</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>황금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사과만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가져가면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>평생</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안하고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놀고먹을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있다는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>거잖아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?!</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>완벽한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>라이프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>위해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사과는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무조건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가진다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_intro_1_106</t>
+  </si>
+  <si>
+    <t>dialogue_intro_1_107</t>
+  </si>
+  <si>
+    <t>Texture2D/Image_Intro_1</t>
+  </si>
+  <si>
+    <t>Texture2D/Image_Intro_2</t>
+  </si>
+  <si>
+    <t>Texture2D/Image_Intro_3</t>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ialogue_play_1_100</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ialogue_play_1_101</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>좋아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목표는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>산</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꼭대기다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>! ...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>근데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>몬스터들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>왜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이렇게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>방해하지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>몬스터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놈들아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>내</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소중한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백수의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>꿈을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>막을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>순</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>!!</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -161,6 +1789,19 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
@@ -233,31 +1874,33 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -541,7 +2184,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>5</v>
@@ -552,7 +2195,7 @@
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="4" t="s">
@@ -732,14 +2375,14 @@
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>2</v>
@@ -758,14 +2401,14 @@
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -784,11 +2427,11 @@
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -809,13 +2452,21 @@
       <c r="R13" s="3"/>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A14" s="7"/>
+      <c r="A14" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="C14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="G14" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="H14" s="7"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
@@ -829,13 +2480,21 @@
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A15" s="7"/>
+      <c r="A15" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
+      <c r="C15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+      <c r="G15" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="H15" s="7"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
@@ -849,79 +2508,135 @@
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A16" s="8"/>
+      <c r="A16" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="C16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+      <c r="G16" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="H16" s="8"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A17" s="9"/>
+      <c r="A17" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="8"/>
+      <c r="C17" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
-      <c r="G17" s="9"/>
+      <c r="G17" s="9" t="s">
+        <v>54</v>
+      </c>
       <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
+      <c r="A18" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
+      <c r="G18" s="9" t="s">
+        <v>54</v>
+      </c>
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="9"/>
+      <c r="A19" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="8"/>
+      <c r="C19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
-      <c r="G19" s="9"/>
+      <c r="G19" s="9" t="s">
+        <v>55</v>
+      </c>
       <c r="H19" s="9"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" s="9"/>
+      <c r="A20" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="8"/>
+      <c r="C20" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
+      <c r="G20" s="9" t="s">
+        <v>55</v>
+      </c>
       <c r="H20" s="9"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="9"/>
+      <c r="A21" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="C21" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
-      <c r="G21" s="9"/>
+      <c r="G21" s="9" t="s">
+        <v>55</v>
+      </c>
       <c r="H21" s="9"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="9"/>
+      <c r="A22" s="12" t="s">
+        <v>56</v>
+      </c>
       <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="9"/>
+      <c r="A23" s="12" t="s">
+        <v>57</v>
+      </c>
       <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="C23" s="13" t="s">
+        <v>59</v>
+      </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
@@ -2014,8 +3729,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="76">
   <si>
     <t>Sound/Voice_Pug_1_I_WantToEatPizza</t>
   </si>
@@ -1395,6 +1395,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">, </t>
     </r>
@@ -1413,6 +1414,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1431,6 +1433,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1449,6 +1452,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1467,6 +1471,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>! ...</t>
     </r>
@@ -1485,6 +1490,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1503,6 +1509,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1521,6 +1528,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1539,6 +1547,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1557,6 +1566,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>?</t>
     </r>
@@ -1570,6 +1580,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1588,6 +1599,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">, </t>
     </r>
@@ -1606,6 +1618,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1624,6 +1637,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">! </t>
     </r>
@@ -1642,6 +1656,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1660,6 +1675,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1678,6 +1694,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1696,6 +1713,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1714,6 +1732,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1732,6 +1751,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1750,9 +1770,685 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>!!</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ialogue_ending_1_100</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_ending_2_100</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>대단한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사과를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구해오다니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밤새도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수수께끼와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정무를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌보아라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!"</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpeakerName</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>국왕</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>주인공</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아니</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>난</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>놀고먹고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>싶었다고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!!"</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>약속대로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>황금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>냥과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>영지를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주겠네</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>역시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백수가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최고야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>!"</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>d</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ialogue_ending_1_101</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_ending_1_101</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_ending_2_101</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Texture2D/Image_EndingA</t>
+  </si>
+  <si>
+    <r>
+      <t>Texture</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>D/Image_EndingA</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Texture2D/Image_EndingB</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1874,7 +2570,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1901,6 +2597,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2119,17 +2817,17 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:R1000"/>
+  <dimension ref="A1:S1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="82.42578125" customWidth="1"/>
-    <col min="4" max="6" width="77.140625" customWidth="1"/>
-    <col min="7" max="8" width="50.7109375" customWidth="1"/>
+    <col min="2" max="3" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="82.42578125" customWidth="1"/>
+    <col min="5" max="7" width="77.140625" customWidth="1"/>
+    <col min="8" max="9" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1">
+    <row r="1" spans="1:19" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -2140,8 +2838,9 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:18" ht="15.75" customHeight="1">
+    <row r="2" spans="1:19" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -2149,25 +2848,28 @@
         <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1">
+    <row r="3" spans="1:19" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -2175,40 +2877,43 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1">
+    <row r="4" spans="1:19" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="5"/>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="3"/>
+      <c r="I4" s="4"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -2218,23 +2923,24 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1">
+    <row r="5" spans="1:19" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B5" s="5"/>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="3"/>
+      <c r="I5" s="4"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -2244,23 +2950,24 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1">
+    <row r="6" spans="1:19" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="5"/>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
@@ -2270,25 +2977,26 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
     </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1">
+    <row r="7" spans="1:19" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="3"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -2298,21 +3006,22 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
     </row>
-    <row r="8" spans="1:18" ht="15.75" customHeight="1">
+    <row r="8" spans="1:19" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="6"/>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="6"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
-      <c r="I8" s="3"/>
+      <c r="I8" s="6"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -2322,23 +3031,24 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
     </row>
-    <row r="9" spans="1:18" ht="15.75" customHeight="1">
+    <row r="9" spans="1:19" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="6"/>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="6"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="6"/>
+      <c r="I9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -2348,21 +3058,22 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
     </row>
-    <row r="10" spans="1:18" ht="15.75" customHeight="1">
+    <row r="10" spans="1:19" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
-      <c r="I10" s="3"/>
+      <c r="I10" s="7"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -2372,23 +3083,24 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
     </row>
-    <row r="11" spans="1:18" ht="15.75" customHeight="1">
+    <row r="11" spans="1:19" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5"/>
+      <c r="D11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="3"/>
+      <c r="I11" s="4"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -2398,23 +3110,24 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:18" ht="15.75" customHeight="1">
+    <row r="12" spans="1:19" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="3"/>
+      <c r="I12" s="4"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -2424,23 +3137,24 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1">
+    <row r="13" spans="1:19" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5"/>
+      <c r="D13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="4"/>
+      <c r="I13" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -2450,25 +3164,28 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:18" ht="15.75" customHeight="1">
+    <row r="14" spans="1:19" ht="15.75" customHeight="1">
       <c r="A14" s="7" t="s">
         <v>36</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="7"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="3"/>
+      <c r="I14" s="7"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -2478,25 +3195,28 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
     </row>
-    <row r="15" spans="1:18" ht="15.75" customHeight="1">
+    <row r="15" spans="1:19" ht="15.75" customHeight="1">
       <c r="A15" s="7" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="7"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="3"/>
+      <c r="I15" s="7"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -2506,184 +3226,245 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
     </row>
-    <row r="16" spans="1:18" ht="15.75" customHeight="1">
+    <row r="16" spans="1:19" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B16" s="8"/>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="8"/>
       <c r="F16" s="8"/>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="8"/>
+      <c r="H16" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+    <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B17" s="9"/>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="8"/>
       <c r="F17" s="8"/>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8"/>
+      <c r="H17" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+    <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B18" s="9"/>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="9"/>
+      <c r="D18" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="8"/>
       <c r="F18" s="8"/>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="8"/>
+      <c r="H18" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+    <row r="19" spans="1:9" ht="15.75" customHeight="1">
       <c r="A19" s="7" t="s">
         <v>40</v>
       </c>
       <c r="B19" s="9"/>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="8"/>
       <c r="F19" s="8"/>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="8"/>
+      <c r="H19" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+    <row r="20" spans="1:9" ht="15.75" customHeight="1">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B20" s="9"/>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="8"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8"/>
+      <c r="H20" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+    <row r="21" spans="1:9" ht="15.75" customHeight="1">
       <c r="A21" s="7" t="s">
         <v>52</v>
       </c>
       <c r="B21" s="9"/>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="8"/>
+      <c r="H21" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1">
       <c r="A22" s="12" t="s">
         <v>56</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="E22" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="8"/>
       <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
+      <c r="G22" s="8"/>
       <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+    <row r="23" spans="1:9" ht="15.75" customHeight="1">
       <c r="A23" s="12" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
-      <c r="G23" s="9"/>
+      <c r="G23" s="8"/>
       <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" s="9"/>
+    <row r="24" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A24" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+      <c r="C24" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>71</v>
+      </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="9"/>
+    <row r="25" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A25" s="12" t="s">
+        <v>70</v>
+      </c>
       <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="8"/>
+      <c r="C25" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>69</v>
+      </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="10"/>
+    <row r="26" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A26" s="12" t="s">
+        <v>61</v>
+      </c>
       <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
+      <c r="C26" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>72</v>
+      </c>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="H26" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="10"/>
     </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
+    <row r="27" spans="1:9" ht="15.75" customHeight="1">
+      <c r="A27" s="12" t="s">
+        <v>72</v>
+      </c>
       <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>67</v>
+      </c>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
+      <c r="H27" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+    <row r="28" spans="1:9" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
@@ -2692,8 +3473,9 @@
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
     </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
@@ -2702,8 +3484,9 @@
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
     </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+    <row r="30" spans="1:9" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -2712,8 +3495,9 @@
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
     </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+    <row r="31" spans="1:9" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
@@ -2722,8 +3506,9 @@
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
     </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1">
+    <row r="32" spans="1:9" ht="15.75" customHeight="1">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -2732,8 +3517,9 @@
       <c r="F32" s="11"/>
       <c r="G32" s="11"/>
       <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:8" ht="15.75" customHeight="1">
+    <row r="33" spans="1:9" ht="15.75" customHeight="1">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -2742,8 +3528,9 @@
       <c r="F33" s="11"/>
       <c r="G33" s="11"/>
       <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" customHeight="1">
+    <row r="34" spans="1:9" ht="15.75" customHeight="1">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -2752,8 +3539,9 @@
       <c r="F34" s="11"/>
       <c r="G34" s="11"/>
       <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
     </row>
-    <row r="35" spans="1:8" ht="15.75" customHeight="1">
+    <row r="35" spans="1:9" ht="15.75" customHeight="1">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -2762,20 +3550,21 @@
       <c r="F35" s="11"/>
       <c r="G35" s="11"/>
       <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
     </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:9" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:9" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
